--- a/artfynd/A 41914-2026 artfynd.xlsx
+++ b/artfynd/A 41914-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,48 +1016,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128291018</v>
+        <v>137520697</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>79536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kallåsen, Dlr</t>
+          <t>Tallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496509</v>
+        <v>496572</v>
       </c>
       <c r="R5" t="n">
-        <v>6772986</v>
+        <v>6773275</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1081,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,24 +1116,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291018</t>
+          <t>https://artportalen.se/Sighting/137520697</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128291020</v>
+        <v>128291018</v>
       </c>
       <c r="B6" t="n">
         <v>57950</v>
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496610</v>
+        <v>496509</v>
       </c>
       <c r="R6" t="n">
-        <v>6773043</v>
+        <v>6772986</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,13 +1239,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291020</t>
+          <t>https://artportalen.se/Sighting/128291018</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128291021</v>
+        <v>128291020</v>
       </c>
       <c r="B7" t="n">
         <v>57950</v>
@@ -1275,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496531</v>
+        <v>496610</v>
       </c>
       <c r="R7" t="n">
-        <v>6773242</v>
+        <v>6773043</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,33 +1351,33 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291021</t>
+          <t>https://artportalen.se/Sighting/128291020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128291013</v>
+        <v>128291021</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1381,24 +1386,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496513</v>
+        <v>496531</v>
       </c>
       <c r="R8" t="n">
-        <v>6773005</v>
+        <v>6773242</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,12 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>äldre spår på gran</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,6 +1462,131 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291021</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128291013</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>496513</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6773005</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre spår på gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128291013</t>
         </is>
@@ -1484,6 +1601,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41914-2026 artfynd.xlsx
+++ b/artfynd/A 41914-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,7 +1019,7 @@
         <v>137520697</v>
       </c>
       <c r="B5" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,32 +1133,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128291018</v>
+        <v>137522702</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496509</v>
+        <v>496547</v>
       </c>
       <c r="R6" t="n">
-        <v>6772986</v>
+        <v>6773387</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1198,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,49 +1228,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291018</t>
+          <t>https://artportalen.se/Sighting/137522702</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128291020</v>
+        <v>137522703</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496610</v>
+        <v>496555</v>
       </c>
       <c r="R7" t="n">
-        <v>6773043</v>
+        <v>6773352</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,22 +1310,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,49 +1340,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291020</t>
+          <t>https://artportalen.se/Sighting/137522703</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128291021</v>
+        <v>137522704</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496531</v>
+        <v>496554</v>
       </c>
       <c r="R8" t="n">
-        <v>6773242</v>
+        <v>6773343</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,73 +1452,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291021</t>
+          <t>https://artportalen.se/Sighting/137522704</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128291013</v>
+        <v>137522705</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496513</v>
+        <v>496537</v>
       </c>
       <c r="R9" t="n">
-        <v>6773005</v>
+        <v>6773322</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,27 +1534,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>äldre spår på gran</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,16 +1564,1272 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522705</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137522706</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>496515</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6773252</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522706</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137522707</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>496521</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6773214</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Med miljöbild</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522707</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137522709</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>496586</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6773232</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522709</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137569241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>496572</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6773320</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569241</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137569242</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>496566</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6773304</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569242</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137569243</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>496566</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6773301</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569243</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128291018</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>496509</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6772986</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291018</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128291020</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>496610</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6773043</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291020</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128291021</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>496531</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6773242</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291021</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137522708</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>496554</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6773225</v>
+      </c>
+      <c r="S19" t="n">
+        <v>7</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522708</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128291013</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>496513</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6773005</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>äldre spår på gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128291013</t>
         </is>
@@ -1602,6 +2845,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
